--- a/Motherboard/Smart Tank PCB (Bill of Materials), v1.2.xlsx
+++ b/Motherboard/Smart Tank PCB (Bill of Materials), v1.2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetilengineering-my.sharepoint.com/personal/gtetil_tetilengineering_onmicrosoft_com/Documents/Documents/Projects/smart-tank-pcb/Motherboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_9B465D10C7D809D967C5F46EE102C561F1367BE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FC78B4A-1480-4D84-8484-5B656E88F6FF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{36074AF1-3788-43E4-96ED-B14B6A5A6D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM v1.2" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="207">
   <si>
     <t>#</t>
   </si>
@@ -536,6 +536,15 @@
     <t>R7, R55, R64, R73, R82, R91</t>
   </si>
   <si>
+    <t>CC1206KRX7R9BB472</t>
+  </si>
+  <si>
+    <t>4700pF 50V CERAMIC CAPACITOR X7R 1206</t>
+  </si>
+  <si>
+    <t>C20, C21, C29, C30, C33, C34, C37, C38, C41, C42, C45, C46</t>
+  </si>
+  <si>
     <t>CC1206KRX7R9BB103</t>
   </si>
   <si>
@@ -560,7 +569,7 @@
     <t>4.7µF 16V CERAMIC CAPACITOR Y5V (F) 1206</t>
   </si>
   <si>
-    <t>C1, C3, C4, C6, C7, C9, C10, C12, C20, C21, C29, C30, C33, C34, C37, C38, C41, C42, C45, C46</t>
+    <t>C1, C3, C4, C6, C7, C9, C10, C12</t>
   </si>
   <si>
     <t>CC1206KKX5R5BB226</t>
@@ -1038,18 +1047,18 @@
   <dimension ref="A1:R948"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="53.140625" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" customWidth="1"/>
-    <col min="10" max="10" width="34.42578125" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="61.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="78" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="26" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1480,11 +1489,11 @@
         <v>Link</v>
       </c>
       <c r="H12" s="10">
-        <v>1.07</v>
+        <v>1.8</v>
       </c>
       <c r="I12" s="10">
         <f t="shared" si="1"/>
-        <v>6.42</v>
+        <v>10.8</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>20</v>
@@ -2689,7 +2698,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="I49" s="10">
-        <f t="shared" ref="I49:I59" si="8">H49*B49</f>
+        <f t="shared" ref="I49:I65" si="8">H49*B49</f>
         <v>0.84000000000000008</v>
       </c>
       <c r="J49" s="8" t="s">
@@ -3081,16 +3090,38 @@
       <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="B60" s="6"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="8"/>
-      <c r="K60" s="6"/>
+      <c r="B60" s="6">
+        <v>12</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60" s="9" t="str">
+        <f>HYPERLINK("http://www.digikey.com/product-detail/en/yageo/CC1206KRX7R9BB472/311-1173-1-ND/303083","Link")</f>
+        <v>Link</v>
+      </c>
+      <c r="H60" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="I60" s="10">
+        <f t="shared" si="8"/>
+        <v>2.2800000000000002</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="L60" s="6"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
@@ -3101,10 +3132,10 @@
         <v>6</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>139</v>
@@ -3119,11 +3150,11 @@
         <v>0.19</v>
       </c>
       <c r="I61" s="10">
-        <f t="shared" ref="I61:I65" si="9">H61*B61</f>
+        <f t="shared" si="8"/>
         <v>1.1400000000000001</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>17</v>
@@ -3138,10 +3169,10 @@
         <v>12</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>139</v>
@@ -3157,11 +3188,11 @@
         <v>0.15</v>
       </c>
       <c r="I62" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>17</v>
@@ -3173,13 +3204,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="6">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>139</v>
@@ -3195,11 +3226,11 @@
         <v>0.21</v>
       </c>
       <c r="I63" s="10">
-        <f t="shared" si="9"/>
-        <v>4.2</v>
+        <f t="shared" si="8"/>
+        <v>1.68</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>17</v>
@@ -3214,10 +3245,10 @@
         <v>4</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>139</v>
@@ -3233,11 +3264,11 @@
         <v>0.3</v>
       </c>
       <c r="I64" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.2</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>17</v>
@@ -3252,13 +3283,13 @@
         <v>1</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>15</v>
@@ -3270,11 +3301,11 @@
         <v>0.42</v>
       </c>
       <c r="I65" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.42</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>17</v>
@@ -3305,16 +3336,16 @@
         <v>19</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G67" s="9" t="str">
         <f>HYPERLINK("http://catalog.pemnet.com/item/uts-and-spacers-standoffs-surface-mount-type-smtso/spacers-standoffs---type-smtsob---unified/smtsob-116-12et","Link")</f>
@@ -3323,7 +3354,7 @@
       <c r="H67" s="10"/>
       <c r="I67" s="10"/>
       <c r="J67" s="8" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>17</v>
@@ -3338,16 +3369,16 @@
         <v>10</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D68" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="E68" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E68" s="8" t="s">
-        <v>185</v>
-      </c>
       <c r="F68" s="8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G68" s="9" t="str">
         <f>HYPERLINK("http://catalog.pemnet.com/item/uts-and-spacers-standoffs-surface-mount-type-smtso/spacers-standoffs---type-smtsob---unified/smtsob-440-12et","Link")</f>
@@ -3356,7 +3387,7 @@
       <c r="H68" s="10"/>
       <c r="I68" s="10"/>
       <c r="J68" s="8" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>17</v>
@@ -3385,16 +3416,16 @@
         <v>1</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G70" s="9" t="str">
         <f>HYPERLINK("http://www.mcmaster.com/#91737a069/=143emwn","Link")</f>
@@ -3404,11 +3435,11 @@
         <v>4.22</v>
       </c>
       <c r="I70" s="10">
-        <f t="shared" ref="I70:I71" si="10">H70*B70</f>
+        <f t="shared" ref="I70:I71" si="9">H70*B70</f>
         <v>4.22</v>
       </c>
       <c r="J70" s="13" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K70" s="6"/>
       <c r="L70" s="6" t="s">
@@ -3423,16 +3454,16 @@
         <v>1</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D71" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="E71" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="E71" s="13" t="s">
-        <v>192</v>
-      </c>
       <c r="F71" s="13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G71" s="9" t="str">
         <f>HYPERLINK("https://www.mcmaster.com/#91772a113/=19kgcxo","Link")</f>
@@ -3442,11 +3473,11 @@
         <v>4.95</v>
       </c>
       <c r="I71" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>4.95</v>
       </c>
       <c r="J71" s="13" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K71" s="6"/>
       <c r="L71" s="6" t="s">
@@ -3476,27 +3507,27 @@
         <v>1</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G73" s="13"/>
       <c r="H73" s="10">
         <v>94.75</v>
       </c>
       <c r="I73" s="10">
-        <f t="shared" ref="I73:I74" si="11">H73*B73</f>
+        <f t="shared" ref="I73:I74" si="10">H73*B73</f>
         <v>94.75</v>
       </c>
       <c r="J73" s="13" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K73" s="6"/>
       <c r="L73" s="6" t="s">
@@ -3511,16 +3542,16 @@
         <v>1</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G74" s="9" t="str">
         <f>HYPERLINK("http://www.mcmaster.com/#91772a110/=143enhs","Link")</f>
@@ -3530,11 +3561,11 @@
         <v>7.54</v>
       </c>
       <c r="I74" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>7.54</v>
       </c>
       <c r="J74" s="13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K74" s="6"/>
       <c r="L74" s="6" t="s">
